--- a/finclass_carteira.xlsx
+++ b/finclass_carteira.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidado" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A - AÇÕES" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R - REAL ESTATE (FUNDOS IMOBILI" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C - CAIXA (RENDA FIXA)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A - ALTERNATIVOS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Consolidado" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="A - AÇÕES" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="R - REAL ESTATE (FUNDOS IMOBILI" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="C - CAIXA (RENDA FIXA)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="A - ALTERNATIVOS" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$J$38</definedName>

--- a/finclass_carteira.xlsx
+++ b/finclass_carteira.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A - ALTERNATIVOS" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$J$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'A - AÇÕES'!$A$1:$D$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$J$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'A - AÇÕES'!$A$1:$D$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'R - REAL ESTATE (FUNDOS IMOBILI'!$A$1:$D$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'C - CAIXA (RENDA FIXA)'!$A$1:$D$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'A - ALTERNATIVOS'!$A$1:$D$14</definedName>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -562,8 +562,8 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2,50%
-R$ 6.250</t>
+          <t>2,00%
+R$ 5.000</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -596,8 +596,8 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2,00%
-R$ 5.000</t>
+          <t>1,50%
+R$ 3.750</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -630,8 +630,8 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>3,50%
-R$ 8.750</t>
+          <t>3,00%
+R$ 7.500</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -704,18 +704,18 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>VAMOS
-VAMO3</t>
+          <t>VALE S.A
+VALE3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>R$ 5,54</t>
+          <t>R$ 83,00</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4.41%</t>
+          <t>7.78%</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
@@ -732,24 +732,24 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2,00%
-R$ 5.000</t>
+          <t>1,50%
+R$ 3.750</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>WIZ CO.
-WIZC3</t>
+          <t>VAMOS
+VAMO3</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>R$ 10,50</t>
+          <t>R$ 5,54</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6.72%</t>
+          <t>4.41%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -761,32 +761,32 @@
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+          <t>A - AÇÕES</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>0,75%
-R$ 1.875</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
+          <t>2,00%
+R$ 5.000</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>WIZ CO.
+WIZC3</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>R$ 85,00</t>
+          <t>R$ 10,50</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11.68%</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>BTG CORPORATE OFFICE FUND FII
-BRCR11</t>
-        </is>
-      </c>
+          <t>6.72%</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
@@ -800,25 +800,25 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2,25%
-R$ 5.625</t>
+          <t>0,75%
+R$ 1.875</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>R$ 8.90</t>
+          <t>R$ 85,00</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13.97%</t>
+          <t>11.68%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>CAPITÂNIA SECURITIES II
-CPTS11</t>
+          <t>BTG CORPORATE OFFICE FUND FII
+BRCR11</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -834,25 +834,25 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1,50%
-R$ 3.750</t>
+          <t>2,25%
+R$ 5.625</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>R$ 81,00</t>
+          <t>R$ 8.90</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13.70%</t>
+          <t>13.97%</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>PÁTRIA SECURITIES
-PSEC11</t>
+          <t>CAPITÂNIA SECURITIES II
+CPTS11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -875,18 +875,18 @@
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 81,00</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7.23%</t>
+          <t>13.70%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>VBI PRIME PROPERTIES
-PVBI11</t>
+          <t>PÁTRIA SECURITIES
+PSEC11</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -902,25 +902,25 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1,00%
-R$ 2.500</t>
+          <t>1,50%
+R$ 3.750</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>R$ 10.45</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11.90%</t>
+          <t>7.23%</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>RIO BRAVO RENDA VAREJO
-RBVA11</t>
+          <t>VBI PRIME PROPERTIES
+PVBI11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -936,25 +936,25 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1,25%
-R$ 3.125</t>
+          <t>1,00%
+R$ 2.500</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>R$ 9,35</t>
+          <t>R$ 10.45</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13.46%</t>
+          <t>11.90%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII
-RBRX11</t>
+          <t>RIO BRAVO RENDA VAREJO
+RBVA11</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -970,25 +970,25 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2,00%
-R$ 5.000</t>
+          <t>1,25%
+R$ 3.125</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>R$ 101.00</t>
+          <t>R$ 9,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12.89%</t>
+          <t>13.46%</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>TRX REAL ESTATE
-TRXF11</t>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII
+RBRX11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -1004,25 +1004,25 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1,00%
-R$ 2.500</t>
+          <t>2,00%
+R$ 5.000</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>R$ 121.00</t>
+          <t>R$ 101.00</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9.35%</t>
+          <t>12.89%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>VINCI SHOPPING CENTERS FII
-VISC11</t>
+          <t>TRX REAL ESTATE
+TRXF11</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1038,25 +1038,25 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1,25%
-R$ 3.125</t>
+          <t>1,00%
+R$ 2.500</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>R$ 111.00</t>
+          <t>R$ 121.00</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9.81%</t>
+          <t>9.35%</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>VINCI LOGÍSTICA
-VILG11</t>
+          <t>VINCI SHOPPING CENTERS FII
+VISC11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1072,25 +1072,25 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1,50%
-R$ 3.750</t>
+          <t>1,25%
+R$ 3.125</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>R$ 95.00</t>
+          <t>R$ 111.00</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12.99%</t>
+          <t>9.81%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>XP CRÉDITO IMOBILIÁRIO
-XPCI11</t>
+          <t>VINCI LOGÍSTICA
+VILG11</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1106,25 +1106,25 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1,00%
-R$ 2.500</t>
+          <t>1,50%
+R$ 3.750</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>R$ 115.00</t>
+          <t>R$ 95.00</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10.70%</t>
+          <t>12.99%</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>XP MALLS
-XPML11</t>
+          <t>XP CRÉDITO IMOBILIÁRIO
+XPCI11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -1135,47 +1135,47 @@
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1,00%
+R$ 2.500</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>R$ 115.00</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>10.70%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>XP MALLS
+XPML11</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>C - CAIXA (RENDA FIXA)</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>15,00%
 R$ 37.500</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA
-Renda Fixa Pós</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Daycoval (103% do CDI), BMG (107% do CDI) e TR é EXCLUSIVO BB</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Daycoval Digital / BMG / BB</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>C - CAIXA (RENDA FIXA)</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>2,50%
-R$ 6.250</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr"/>
@@ -1184,18 +1184,18 @@
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>CPTI11 (CAPITÂNIA INFRA)
-Renda Fixa Dinâmica</t>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA
+Renda Fixa Pós</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>P / VP até 1,05</t>
+          <t>Daycoval (103% do CDI), BMG (107% do CDI) e TR é EXCLUSIVO BB</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Home Broker</t>
+          <t>Daycoval Digital / BMG / BB</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -1208,8 +1208,8 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>5,00%
-R$ 12.500</t>
+          <t>2,50%
+R$ 6.250</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
@@ -1218,13 +1218,13 @@
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>ETF IRFM11 OU ETF IDKA11
+          <t>CPTI11 (CAPITÂNIA INFRA)
 Renda Fixa Dinâmica</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>No preço atual</t>
+          <t>P / VP até 1,05</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1242,8 +1242,8 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>2,50%
-R$ 6.250</t>
+          <t>5,00%
+R$ 12.500</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr"/>
@@ -1252,13 +1252,13 @@
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>JURO11 (SPARTA INFRA RENDA FIXA)
+          <t>ETF IRFM11 OU ETF IDKA11
 Renda Fixa Dinâmica</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>P / VP até 1,035</t>
+          <t>No preço atual</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1286,13 +1286,13 @@
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>KDIF11 (KINEA INFRA RENDA FIXA)
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)
 Renda Fixa Dinâmica</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>P / VP até 1,05</t>
+          <t>P / VP até 1,035</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1310,8 +1310,8 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>7,50%
-R$ 18.750</t>
+          <t>2,50%
+R$ 6.250</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr"/>
@@ -1320,18 +1320,18 @@
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>TESOURO IPCA 2050
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)
 Renda Fixa Dinâmica</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>No mínimo IPCA + 6,5%</t>
+          <t>P / VP até 1,05</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Todas as plataformas</t>
+          <t>Home Broker</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -1339,13 +1339,13 @@
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>A - ALTERNATIVOS</t>
+          <t>C - CAIXA (RENDA FIXA)</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>3,00%
-R$ 7.500</t>
+          <t>7,50%
+R$ 18.750</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
@@ -1354,21 +1354,21 @@
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>ABSOLUTE VERTEX
-Multimercado</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
+          <t>TESOURO IPCA 2050
+Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>No mínimo IPCA + 6,5%</t>
+        </is>
+      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Ágora, C6, BTG, Inter, Rico, Safra e XP</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>R$ 500,00</t>
-        </is>
-      </c>
+          <t>Todas as plataformas</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -1388,14 +1388,14 @@
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>GENOA CAPITAL RADAR
+          <t>ABSOLUTE VERTEX
 Multimercado</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Ágora, Banco Inter, BTG, Genial, Guide, Itaú, NuInvest, Pi/Toro, Safra e XP</t>
+          <t>Ágora, C6, BTG, Inter, Rico, Safra e XP</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1422,14 +1422,14 @@
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>IBIUNA HEDGE ST
+          <t>GENOA CAPITAL RADAR
 Multimercado</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Ágora, Banco Inter, BB, Bradesco, BTG, C6, Daycoval Digital, Genial, Guide, NIinvest, Itaú, Pi/Touro, XP, Safra e Santander</t>
+          <t>Ágora, Banco Inter, BTG, Genial, Guide, Itaú, NuInvest, Pi/Toro, Safra e XP</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -1456,19 +1456,19 @@
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>KAPITALO KAPPA (OU ZETA)
+          <t>IBIUNA HEDGE ST
 Multimercado</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Ágora, BB, Bradesco, Banco Inter, BTG, C6, Daycoval Digital, Genial, Itaú, NuInvest, Pi/Toro, Rico e XP</t>
+          <t>Ágora, Banco Inter, BB, Bradesco, BTG, C6, Daycoval Digital, Genial, Guide, NIinvest, Itaú, Pi/Touro, XP, Safra e Santander</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.000,00</t>
+          <t>R$ 500,00</t>
         </is>
       </c>
     </row>
@@ -1480,8 +1480,8 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2,50%
-R$ 6.250</t>
+          <t>3,00%
+R$ 7.500</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
@@ -1490,19 +1490,19 @@
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>ALUG11 (no exterior é o VNQ)
-Internacional</t>
+          <t>KAPITALO KAPPA (OU ZETA)
+Multimercado</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Home broker</t>
+          <t>Ágora, BB, Bradesco, Banco Inter, BTG, C6, Daycoval Digital, Genial, Itaú, NuInvest, Pi/Toro, Rico e XP</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 1.000,00</t>
         </is>
       </c>
     </row>
@@ -1514,8 +1514,8 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1,00%
-R$ 2.500</t>
+          <t>2,50%
+R$ 6.250</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr"/>
@@ -1524,7 +1524,7 @@
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>BNDX11 (no exterior é o BNDX)
+          <t>ALUG11 (no exterior é o VNQ)
 Internacional</t>
         </is>
       </c>
@@ -1548,8 +1548,8 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>3,00%
-R$ 7.500</t>
+          <t>1,00%
+R$ 2.500</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
@@ -1558,7 +1558,7 @@
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>GOLD11 (no exterior é o IAU)
+          <t>BNDX11 (no exterior é o BNDX)
 Internacional</t>
         </is>
       </c>
@@ -1582,8 +1582,8 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>2,00%
-R$ 5.000</t>
+          <t>3,00%
+R$ 7.500</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr"/>
@@ -1592,19 +1592,19 @@
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>MS GLOBAL OPPORTUNITIES DÓLAR
-Internacional (33.913.562/0001-85)</t>
+          <t>GOLD11 (no exterior é o IAU)
+Internacional</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>Home broker</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>R$ 500,00</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1616,8 +1616,8 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>3,00%
-R$ 7.500</t>
+          <t>2,00%
+R$ 5.000</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
@@ -1626,19 +1626,19 @@
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>USDB11 (no exterior é o BND)
-Internacional</t>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR
+Internacional (33.913.562/0001-85)</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Home broker</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 500,00</t>
         </is>
       </c>
     </row>
@@ -1650,8 +1650,8 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>8,50%
-R$ 21.250</t>
+          <t>3,00%
+R$ 7.500</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr"/>
@@ -1660,7 +1660,7 @@
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>WRLD11 (no exterior é o VT)
+          <t>USDB11 (no exterior é o BND)
 Internacional</t>
         </is>
       </c>
@@ -1684,8 +1684,8 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1,00%
-R$ 2.500</t>
+          <t>8,50%
+R$ 21.250</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr"/>
@@ -1694,14 +1694,14 @@
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>BITCOIN
-Teses alternativas</t>
+          <t>WRLD11 (no exterior é o VT)
+Internacional</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Binance, Mercado Bitcoin, Foxbit e Bitybank</t>
+          <t>Home broker</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -1728,14 +1728,14 @@
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>HTEK11
+          <t>BITCOIN
 Teses alternativas</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Home broker</t>
+          <t>Binance, Mercado Bitcoin e Foxbit</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -1762,24 +1762,58 @@
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t>HTEK11
+Teses alternativas</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Home broker</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>1,00%
+R$ 2.500</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
           <t>NUCL11
 Teses alternativas</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>Home broker</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J38"/>
+  <autoFilter ref="A1:J39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1790,7 +1824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1848,8 +1882,8 @@
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2,50%
-R$ 6.250</t>
+          <t>2,00%
+R$ 5.000</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1872,125 +1906,149 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>1,50%
+R$ 3.750</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER
+KEPL3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>R$ 9,55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10.77%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>3,00%
+R$ 7.500</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>PRIO
+PRIO3</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,24</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>2,00%
 R$ 5.000</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>KEPLER WEBER
-KEPL3</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>R$ 9,55</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10.77%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>3,50%
-R$ 8.750</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>PRIO
-PRIO3</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>R$ 69,24</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA
+SLCE3</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>R$ 23,28</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2,00%
 R$ 5.000</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SLC AGRÍCOLA
-SLCE3</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>R$ 23,28</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7.97%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>VALE S.A
+VALE3</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>R$ 83,00</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7.78%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>1,50%
+R$ 3.750</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>VAMOS
+VAMO3</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>R$ 5,54</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2,00%
 R$ 5.000</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>VAMOS
-VAMO3</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>R$ 5,54</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4.41%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2,00%
-R$ 5.000</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>WIZ CO.
 WIZC3</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>R$ 10,50</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>6.72%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D8"/>
+  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2786,7 +2844,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Binance, Mercado Bitcoin, Foxbit e Bitybank</t>
+          <t>Binance, Mercado Bitcoin e Foxbit</t>
         </is>
       </c>
     </row>

--- a/finclass_carteira.xlsx
+++ b/finclass_carteira.xlsx
@@ -875,18 +875,18 @@
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>R$ 81,00</t>
+          <t>Em revisão</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13.70%</t>
+          <t>Em revisão</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
           <t>PÁTRIA SECURITIES
-PSEC11</t>
+Em revisão</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -2148,17 +2148,17 @@
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>PÁTRIA SECURITIES
-PSEC11</t>
+Em revisão</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>13.70%</t>
+          <t>Em revisão</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>R$ 81,00</t>
+          <t>Em revisão</t>
         </is>
       </c>
     </row>

--- a/finclass_carteira.xlsx
+++ b/finclass_carteira.xlsx
@@ -637,12 +637,12 @@
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>PRIO
-PRIO3</t>
+Em revisão</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,24</t>
+          <t>Em revisão</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -739,17 +739,17 @@
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>VAMOS
-VAMO3</t>
+Em revisão</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>R$ 5,54</t>
+          <t>Em revisão</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4.41%</t>
+          <t>2.48%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -773,12 +773,12 @@
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>WIZ CO.
-WIZC3</t>
+Em revisão</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>R$ 10,50</t>
+          <t>Em revisão</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>PRIO
-PRIO3</t>
+Em revisão</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,24</t>
+          <t>Em revisão</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2009,17 +2009,17 @@
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>VAMOS
-VAMO3</t>
+Em revisão</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>R$ 5,54</t>
+          <t>Em revisão</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4.41%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
@@ -2033,12 +2033,12 @@
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>WIZ CO.
-WIZC3</t>
+Em revisão</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>R$ 10,50</t>
+          <t>Em revisão</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">

--- a/finclass_carteira.xlsx
+++ b/finclass_carteira.xlsx
@@ -773,12 +773,12 @@
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>WIZ CO.
-Em revisão</t>
+WIZC3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Em revisão</t>
+          <t>R$ 7,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>WIZ CO.
-Em revisão</t>
+WIZC3</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Em revisão</t>
+          <t>R$ 7,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">

--- a/finclass_carteira.xlsx
+++ b/finclass_carteira.xlsx
@@ -1360,7 +1360,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>No mínimo IPCA + 6,5%</t>
+          <t>No mínimo IPCA + 6,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>No mínimo IPCA + 6,5%</t>
+          <t>No mínimo IPCA + 6,4%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">

--- a/finclass_carteira.xlsx
+++ b/finclass_carteira.xlsx
@@ -637,12 +637,12 @@
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>PRIO
-Em revisão</t>
+PRIO3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Em revisão</t>
+          <t>R$ 69,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -739,12 +739,12 @@
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>VAMOS
-Em revisão</t>
+VAMO3</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Em revisão</t>
+          <t>R$ 5,54</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>PRIO
-Em revisão</t>
+PRIO3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Em revisão</t>
+          <t>R$ 69,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2009,12 +2009,12 @@
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>VAMOS
-Em revisão</t>
+VAMO3</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Em revisão</t>
+          <t>R$ 5,54</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
